--- a/LocalData/pricing.xlsx
+++ b/LocalData/pricing.xlsx
@@ -33107,7 +33107,7 @@
         <x:v>1395</x:v>
       </x:c>
       <x:c r="D118" s="85">
-        <x:v>273</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="E118" s="69"/>
     </x:row>

--- a/LocalData/pricing.xlsx
+++ b/LocalData/pricing.xlsx
@@ -17899,7 +17899,7 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="D244" s="4">
-        <x:v>799</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="E244" s="10"/>
     </x:row>
@@ -26926,7 +26926,7 @@
         <x:v>2164</x:v>
       </x:c>
       <x:c r="D109" s="35">
-        <x:v>799</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="E109" s="69"/>
     </x:row>
